--- a/BeatnotePostHotCell/May29,2026/Fit_ResultMay29.xlsx
+++ b/BeatnotePostHotCell/May29,2026/Fit_ResultMay29.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\May29,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\May29,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB524CC2-A34D-47D0-A3EF-E05AA70D3B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF12104-E867-4239-AE45-E00F4E58CE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
-    <sheet name="456" sheetId="1" r:id="rId1"/>
-    <sheet name="894" sheetId="2" r:id="rId2"/>
+    <sheet name="894" sheetId="2" r:id="rId1"/>
+    <sheet name="456" sheetId="1" r:id="rId2"/>
     <sheet name="AbsCoef" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -92,7 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,11 +460,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,187 +490,173 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>0.18265936593662399</v>
+        <v>8.5185527459719204</v>
       </c>
       <c r="C2" s="1">
-        <v>1.4877326126488299</v>
-      </c>
-      <c r="D2" s="2">
-        <v>-7.8606714259309805E-5</v>
+        <v>1.30768911039352</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-1.7519009934804E-3</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.52824147062618E-4</v>
+        <v>1.79595974081839</v>
       </c>
       <c r="F2" s="1">
-        <v>3.32017316060662</v>
+        <v>63.052313479327303</v>
       </c>
       <c r="G2" s="1">
-        <v>63.000378205488197</v>
-      </c>
-      <c r="H2" s="1">
-        <v>5.7858330859716597E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>4.02802478036137E-3</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>0.17720413354468001</v>
+        <v>8.5260980793629599</v>
       </c>
       <c r="C3" s="1">
-        <v>1.4845226781956</v>
+        <v>1.30890643847441</v>
       </c>
       <c r="D3" s="1">
-        <v>-1.49694397701938E-4</v>
+        <v>-2.41415382156297E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.2469522433165999E-4</v>
+        <v>1.7961478609845301</v>
       </c>
       <c r="F3" s="1">
-        <v>2.8090461789423</v>
+        <v>63.067108228741198</v>
       </c>
       <c r="G3" s="1">
-        <v>61.067574120001197</v>
-      </c>
-      <c r="H3" s="1">
-        <v>5.7857693507789795E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>3.0086494483874101E-3</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>0.183642067498062</v>
+        <v>8.4894844505278897</v>
       </c>
       <c r="C4" s="1">
-        <v>1.4855722322614699</v>
+        <v>1.30989106904372</v>
       </c>
       <c r="D4" s="1">
-        <v>2.66234961171399E-4</v>
+        <v>-2.5258667783627699E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>-2.1731793057564301E-4</v>
+        <v>1.7934615456482501</v>
       </c>
       <c r="F4" s="1">
-        <v>3.0689498839455198</v>
+        <v>63.086491919662997</v>
       </c>
       <c r="G4" s="1">
-        <v>63.065815402769204</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.1570903059425E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>4.0387138323088904E-3</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>0.18126642652018499</v>
+        <v>8.5701060942568006</v>
       </c>
       <c r="C5" s="1">
-        <v>1.49264476444841</v>
+        <v>1.3059708321592001</v>
       </c>
       <c r="D5" s="1">
-        <v>-7.2092790463104597E-4</v>
+        <v>-4.7429139589702596E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>-1.01748508866653E-4</v>
+        <v>2.0428497810705402</v>
       </c>
       <c r="F5" s="1">
-        <v>3.3174561482465501</v>
+        <v>61.3903751857939</v>
       </c>
       <c r="G5" s="1">
-        <v>62.987432350854903</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.0631471391712799E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.29497040199214E-3</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>0.17863631678412401</v>
+        <v>8.5447049809269604</v>
       </c>
       <c r="C6" s="1">
-        <v>1.49402339118087</v>
+        <v>1.3029790504283001</v>
       </c>
       <c r="D6" s="1">
-        <v>-1.91139794978022E-3</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3.2122409959086401E-5</v>
+        <v>-4.1179199203563201E-3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.0432263582871402</v>
       </c>
       <c r="F6" s="1">
-        <v>3.3199021895854801</v>
+        <v>61.015983640144498</v>
       </c>
       <c r="G6" s="1">
-        <v>61.013457666794501</v>
-      </c>
-      <c r="H6" s="1">
-        <v>8.53441291013585E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.2873004957080102E-3</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>0.18200369359492499</v>
+        <v>8.4017872832855591</v>
       </c>
       <c r="C7" s="1">
-        <v>1.4871376527873701</v>
-      </c>
-      <c r="D7" s="2">
-        <v>4.6823184571633797E-5</v>
+        <v>1.31517154418531</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-2.3480350309565698E-3</v>
       </c>
       <c r="E7" s="1">
-        <v>-1.50075865376724E-4</v>
+        <v>1.79190161108519</v>
       </c>
       <c r="F7" s="1">
-        <v>3.31818268929247</v>
+        <v>62.982569369431303</v>
       </c>
       <c r="G7" s="1">
-        <v>62.977300845906299</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.15715382441481E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>4.13129745915652E-3</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>0.18140063454570701</v>
+        <v>8.4035403242380404</v>
       </c>
       <c r="C8" s="1">
-        <v>1.48785461806069</v>
+        <v>1.3076365891608099</v>
       </c>
       <c r="D8" s="1">
-        <v>-2.4885625990889903E-4</v>
+        <v>5.1522845267592101E-4</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.25193803093727E-4</v>
+        <v>1.79505584511143</v>
       </c>
       <c r="F8" s="1">
-        <v>3.3122882818487702</v>
+        <v>63.047307788104398</v>
       </c>
       <c r="G8" s="1">
-        <v>61.0424740022058</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6.4418950526841899E-4</v>
-      </c>
+        <v>2.9101679250182898E-3</v>
+      </c>
+      <c r="H8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -680,11 +664,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -710,173 +694,187 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>8.5185527459719204</v>
+        <v>0.142207734258748</v>
       </c>
       <c r="C2" s="1">
-        <v>1.30768911039352</v>
-      </c>
-      <c r="D2" s="1">
-        <v>-1.7519009934804E-3</v>
+        <v>1.4877326126488299</v>
+      </c>
+      <c r="D2" s="2">
+        <v>-7.8606714259309805E-5</v>
       </c>
       <c r="E2" s="1">
-        <v>1.79595974081839</v>
+        <v>-1.52824147062618E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>63.052313479327303</v>
+        <v>3.2590006911493798</v>
       </c>
       <c r="G2" s="1">
-        <v>4.02802478036137E-3</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>62.045153212480997</v>
+      </c>
+      <c r="H2" s="1">
+        <v>7.5219137924903098E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <v>8.5260980793629599</v>
+        <v>0.13801119003128501</v>
       </c>
       <c r="C3" s="1">
-        <v>1.30890643847441</v>
+        <v>1.4845226781956</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.41415382156297E-3</v>
+        <v>-1.49694397701938E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>1.7961478609845301</v>
+        <v>-1.2469522433165999E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>63.067108228741198</v>
+        <v>2.7478697567358399</v>
       </c>
       <c r="G3" s="1">
-        <v>3.0086494483874101E-3</v>
-      </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61.073140422654902</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6.0012261058330801E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>8.4894844505278897</v>
+        <v>0.14302506923553299</v>
       </c>
       <c r="C4" s="1">
-        <v>1.30989106904372</v>
+        <v>1.4855722322614699</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.5258667783627699E-3</v>
+        <v>2.66234961171399E-4</v>
       </c>
       <c r="E4" s="1">
-        <v>1.7934615456482501</v>
+        <v>-2.1731793057564301E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>63.086491919662997</v>
+        <v>3.0077918923300699</v>
       </c>
       <c r="G4" s="1">
-        <v>4.0387138323088904E-3</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>63.065902683496397</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.1548814278238299E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>8.5701060942568006</v>
+        <v>0.141175020925183</v>
       </c>
       <c r="C5" s="1">
-        <v>1.3059708321592001</v>
+        <v>1.49264476444841</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.7429139589702596E-3</v>
+        <v>-7.2092790463104597E-4</v>
       </c>
       <c r="E5" s="1">
-        <v>2.0428497810705402</v>
+        <v>-1.01748508866653E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>61.3903751857939</v>
+        <v>3.2562918645096102</v>
       </c>
       <c r="G5" s="1">
-        <v>2.29497040199214E-3</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>62.968910144931797</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.08872239781116E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>8.5447049809269604</v>
+        <v>0.13910706901585701</v>
       </c>
       <c r="C6" s="1">
-        <v>1.3029790504283001</v>
+        <v>1.49402339118087</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.1179199203563201E-3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>2.0432263582871402</v>
+        <v>-1.91139794978022E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.2122409959086401E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>61.015983640144498</v>
+        <v>3.2587605424766299</v>
       </c>
       <c r="G6" s="1">
-        <v>2.2873004957080102E-3</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>61.230150002296</v>
+      </c>
+      <c r="H6" s="1">
+        <v>7.1234902124195105E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>8.4017872832855591</v>
+        <v>0.14173595580689399</v>
       </c>
       <c r="C7" s="1">
-        <v>1.31517154418531</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-2.3480350309565698E-3</v>
+        <v>1.4871376527873701</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4.6823184571633797E-5</v>
       </c>
       <c r="E7" s="1">
-        <v>1.79190161108519</v>
+        <v>-1.50075865376724E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>62.982569369431303</v>
+        <v>3.2570046692763701</v>
       </c>
       <c r="G7" s="1">
-        <v>4.13129745915652E-3</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>62.962828720504497</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.12240668150126E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>8.4035403242380404</v>
+        <v>0.141258173819516</v>
       </c>
       <c r="C8" s="1">
-        <v>1.3076365891608099</v>
+        <v>1.48785461806069</v>
       </c>
       <c r="D8" s="1">
-        <v>5.1522845267592101E-4</v>
+        <v>-2.4885625990889903E-4</v>
       </c>
       <c r="E8" s="1">
-        <v>1.79505584511143</v>
+        <v>-1.25193803093727E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>63.047307788104398</v>
+        <v>3.2511240518968898</v>
       </c>
       <c r="G8" s="1">
-        <v>2.9101679250182898E-3</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>61.008319814915303</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5.9045482025522498E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -885,9 +883,98 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="42.75">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>8.5185527459719204</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.142207734258748</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="42.75">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>8.5260980793629599</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.13801119003128501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="42.75">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>8.4894844505278897</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.14302506923553299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>8.5701060942568006</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.141175020925183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="42.75">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8.5447049809269604</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.13910706901585701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="42.75">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1">
+        <v>8.4017872832855591</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.14173595580689399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="42.75">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>8.4035403242380404</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.141258173819516</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>